--- a/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUxValidation_FigureData_calcs.xlsx
+++ b/AVIATIONprocessing/SliceVelocityValidation/SSWT_SliceUxValidation_FigureData_calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Boller CFD\GitHub\CFDPostprocessingCodes\AVIATIONprocessing\SliceVelocityValidation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AA525D-CF4A-4091-9F88-0977640B2322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68914E37-A697-418F-A51F-7021FC26D209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5685" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{12DF1E63-F8AF-48B4-87CD-AC55BD68FC80}"/>
   </bookViews>
